--- a/term2/lab11/task4_14.xlsx
+++ b/term2/lab11/task4_14.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timof\Documents\Visual Studio Code\BasicsOfAlgorithmisationAndProgramming\term2\lab11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timofejmarusko/Documents/VisualStudioCodeRepos/BasicsOfAlgorithmisationAndProgramming/term2/lab11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EFE60E-EBF2-4EFB-B92E-6832758F5F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC27E52E-CDB9-D84B-919B-D3F570B4E515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="10440" windowWidth="26010" windowHeight="10545" xr2:uid="{7160D8B7-3DE7-42EB-B79A-D65F57C714A2}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="17040" windowHeight="9780" xr2:uid="{7160D8B7-3DE7-42EB-B79A-D65F57C714A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -2511,15 +2511,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25E462-662D-40CD-8EAB-8663B36CF6AF}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="27.85546875" customWidth="1"/>
+    <col min="14" max="14" width="27.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>100</v>
       </c>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>500</v>
       </c>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>5000</v>
       </c>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>50000</v>
       </c>
@@ -2581,22 +2581,22 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1000</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>25.001000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>5000</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>20.077999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>10000</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>20.7362</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>50000</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>20.337</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>100000</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>500000</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>21.91</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
     </row>
